--- a/data/trans_camb/IP1006-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 0,0</t>
+          <t>-8,02; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 0,0</t>
+          <t>-7,22; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 11,17</t>
+          <t>0,98; 11,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,79</t>
+          <t>-1,3; 4,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,0</t>
+          <t>-3,6; 0,0</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,0</t>
+          <t>-4,06; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,0</t>
+          <t>-3,84; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,0</t>
+          <t>-1,58; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,6</t>
+          <t>-0,96; 0,59</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,86</t>
+          <t>-5,8; 2,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,0</t>
+          <t>-6,46; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,46</t>
+          <t>-2,65; 1,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,49</t>
+          <t>-3,3; 1,5</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,81</t>
+          <t>-1,23; 0,82</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,66</t>
+          <t>-1,62; 0,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,4</t>
+          <t>-2,37; 0,73</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,71</t>
+          <t>-2,14; 0,68</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,58</t>
+          <t>-1,25; 0,59</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,44</t>
+          <t>-1,31; 0,45</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,28</t>
+          <t>-0,64; 0,28</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,53</t>
+          <t>-0,5; 0,5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,22</t>
+          <t>-0,06; 1,21</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,42</t>
+          <t>-0,5; 0,37</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,59</t>
+          <t>-0,21; 0,58</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,37</t>
+          <t>-0,34; 0,32</t>
         </is>
       </c>
     </row>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,57; 484,36</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 1173,73</t>
+          <t>-43,27; 1169,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-41,77; 337,14</t>
+          <t>-54,41; 346,45</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 237,81</t>
+          <t>-71,35; 206,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Provincia-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 0,0</t>
+          <t>-7,43; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,0</t>
+          <t>-7,7; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 11,05</t>
+          <t>0,99; 10,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,41</t>
+          <t>-1,09; 4,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,0</t>
+          <t>-3,29; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,0</t>
+          <t>-3,62; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,0</t>
+          <t>-1,95; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,59</t>
+          <t>-0,95; 0,6</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 4,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 2,84</t>
+          <t>-5,02; 2,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 0,0</t>
+          <t>-7,6; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,46</t>
+          <t>-2,6; 1,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,5</t>
+          <t>-2,86; 1,48</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
     </row>
@@ -1728,27 +1728,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,66</t>
+          <t>-1,29; 0,65</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,73</t>
+          <t>-2,11; 0,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,68</t>
+          <t>-2,52; 0,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,59</t>
+          <t>-1,27; 0,59</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,45</t>
+          <t>-1,3; 0,45</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,28</t>
+          <t>-0,64; 0,21</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,5</t>
+          <t>-0,5; 0,56</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,21</t>
+          <t>-0,03; 1,25</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,37</t>
+          <t>-0,5; 0,41</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,58</t>
+          <t>-0,2; 0,6</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,32</t>
+          <t>-0,38; 0,32</t>
         </is>
       </c>
     </row>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 484,36</t>
+          <t>-87,51; 541,62</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 1169,96</t>
+          <t>-37,87; 1571,15</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 346,45</t>
+          <t>-46,99; 374,3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-71,35; 206,39</t>
+          <t>-72,96; 223,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-2,3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-2,3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,0</t>
+          <t>0,96; 11,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,84</t>
+          <t>-7,79; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,98; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,72</t>
+          <t>-1,39; 4,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,0</t>
+          <t>-3,58; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,57</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,26</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>-3,27; 0,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>-3,29; 0,0</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,45</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,0</t>
+          <t>-1,77; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,6</t>
+          <t>-0,96; 0,6</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,96</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,14</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,61</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,52</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,91; 2,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>-6,48; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 0,0</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,46</t>
+          <t>-3,31; 1,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,48</t>
+          <t>-2,81; 1,49</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-11,88%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-11,88%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,49</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,44</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,47</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,08</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,47</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,82</t>
+          <t>-2,13; 0,4</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,65</t>
+          <t>-2,2; 0,71</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,77</t>
+          <t>-1,23; 0,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,37</t>
+          <t>-1,24; 0,66</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,59</t>
+          <t>-1,25; 0,58</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,45</t>
+          <t>-1,37; 0,44</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-52,88%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-56,44%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-1,3%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-19,7%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-52,88%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-56,44%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-0,18</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>0,01</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,21</t>
+          <t>-0,14; 1,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,56</t>
+          <t>-0,51; 0,42</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,25</t>
+          <t>-0,66; 0,28</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,41</t>
+          <t>-0,5; 0,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,6</t>
+          <t>-0,18; 0,59</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,32</t>
+          <t>-0,33; 0,37</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>170,87%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-7,64%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-48,35%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>170,87%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-7,64%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-54,75; 1173,73</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 541,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 1571,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 374,3</t>
+          <t>-41,77; 337,14</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-72,96; 223,54</t>
+          <t>-71,43; 237,81</t>
         </is>
       </c>
     </row>
